--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -608,6 +608,273 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>noon</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>INV000002</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:15:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>GENERAL PURPOSE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>INV000003</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:24:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Grease (Lithium-based) Extended Life</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>BIS 12203</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>INV000001</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Batch: BIS 12203</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:26:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>noon</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>INV000002</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:26:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>GENERAL PURPOSE</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>INV000003</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:26:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -448,12 +448,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -875,6 +875,69 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>** Grease Extended Life (Lithium-based)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>45883</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>INV000007</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: 45883</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:39:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -448,11 +448,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -938,6 +938,57 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>** Fevicol (partially visible as "...COL" with the elephant logo)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>INV000008</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:51:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -448,12 +448,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="83" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -463,7 +463,7 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
@@ -989,6 +989,486 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Product Item</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>INV000009</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 06:38:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Procedure Drapes Hip U Drape Eco E511 Size : 240 x 225 an, U Cut 20 + 30 cm &amp; On</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2031-05-01</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Expiry</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>INV000010</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: Expiry</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ROMO vec SETO CLOSED WOUND DRAINAGE SYSTEM EGS-5002 S NET QUANTITY.: I UNIT Manu</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>INV000011</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:09:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Procedure Drapes - Hip U Drape Eco E511</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1169</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2031-05-01</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2606AC0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>INV000012</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: 2606AC0</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ROMO VAC SET® (Closed Wound Drainage System)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2031-02-01</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>G26C010052</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>INV000013</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: G26C010052</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:26:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2797 1262 Eysins, Switzerland En#nd. RG41 STS LOT 0086 (01 (11)251201 (17)300928</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0086</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>INV000014</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: 0086</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>NEBULIZER ACCESSORIES KIT CONSISTS OF: (l) Nebulizer Chamber-I Unit (11) Soft. F</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2029-11-01</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>G24L040664</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>INV000015</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: G24L040664</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:38:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ZBATCH NO.: G24C010837 MFG. DT. : 03-2024 EXP. CT. : 02-2029 1 UNITZ61.00 CURREN</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2029-02-01</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>G24C010837</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>INV000016</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Batch/SKU: G24C010837</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 08:44:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
